--- a/insurance_data/4_life/home_fire/extracted_data.xlsx
+++ b/insurance_data/4_life/home_fire/extracted_data.xlsx
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한화 다이렉트 119주택화재보험 (무)2601</t>
+          <t>한화 다이렉트 119주택화재보험 (무)2604</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>581 원</t>
+          <t>591 원</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>581 원</t>
+          <t>591 원</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>한화 다이렉트 119주택화재보험 (무)2601</t>
+          <t>한화 다이렉트 119주택화재보험 (무)2604</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>591</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>591</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한화 다이렉트 119주택화재보험 (무)2601</t>
+          <t>한화 다이렉트 119주택화재보험 (무)2604</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한화 다이렉트 119주택화재보험 (무)2601</t>
+          <t>한화 다이렉트 119주택화재보험 (무)2604</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한화 다이렉트 119주택화재보험 (무)2601</t>
+          <t>한화 다이렉트 119주택화재보험 (무)2604</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한화 다이렉트 119주택화재보험 (무)2601</t>
+          <t>한화 다이렉트 119주택화재보험 (무)2604</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 화재보험(2601)</t>
+          <t>무배당 하나더퍼스트 화재보험(2604)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>762 원</t>
+          <t>803 원</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>762 원</t>
+          <t>803 원</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 화재보험(2601)</t>
+          <t>무배당 하나더퍼스트 화재보험(2604)</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2677,22 +2677,22 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>803</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>803</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>133.1</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>133.1</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr"/>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 화재보험(2601)</t>
+          <t>무배당 하나더퍼스트 화재보험(2604)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 화재보험(2601)</t>
+          <t>무배당 하나더퍼스트 화재보험(2604)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 화재보험(2601)</t>
+          <t>무배당 하나더퍼스트 화재보험(2604)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>무배당 하나더퍼스트 화재보험(2601)</t>
+          <t>무배당 하나더퍼스트 화재보험(2604)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -7486,32 +7486,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>가족화재벌금</t>
+          <t>뇌혈관질환(Ⅰ)진단(갱신형)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>형법 제170조(실화) 혹은 동법 171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
+          <t>뇌혈관질환(Ⅰ)으로 진단확정된 경우</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2000만원</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2000만원</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>299 원</t>
+          <t>14,925 원</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>299 원</t>
+          <t>13,818 원</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -7533,42 +7533,42 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>가족화재벌금</t>
+          <t>뇌혈관질환(Ⅰ)진단(갱신형)</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>형법 제170조(실화) 혹은 동법 171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
+          <t>뇌혈관질환(Ⅰ)으로 진단확정된 경우</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2000만원</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>14,925</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>13,818</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>101.4</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.3</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr"/>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7610,16 +7610,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>건물복구비용지원(주택, 화재)</t>
+          <t>보험료납입면제대상(갱신형)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>화재로 인해 보험증권에 가입한 건물에 손해 및 소방, 피난손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+          <t>상해 또는 질병으로 장해지급률이 80%이상에 해당하는 경우 또는 보장개시일 이후 ‘암’(‘유사암’ 제외) 또는‘뇌졸중’또는‘급성심근경색증’또는‘말기신부전증’또는‘말기간경화’또는‘말기폐질환’으로 진단 확정된 경우</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1백만원</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1백만원</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -7638,15 +7646,19 @@
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr">
         <is>
-          <t>건물복구비용지원(주택, 화재)</t>
+          <t>보험료납입면제대상(갱신형)</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>화재로 인해 보험증권에 가입한 건물에 손해 및 소방, 피난손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr"/>
+          <t>상해 또는 질병으로 장해지급률이 80%이상에 해당하는 경우 또는 보장개시일 이후 ‘암’(‘유사암’ 제외) 또는‘뇌졸중’또는‘급성심근경색증’또는‘말기신부전증’또는‘말기간경화’또는‘말기폐질환’으로 진단 확정된 경우</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>1백만원</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -7680,7 +7692,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7690,22 +7702,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>주택임시거주비Ⅱ(1-90일, 화재)</t>
+          <t>상해사망(갱신형)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>화재, 폭발, 파열로 인해 보험증권에 기재된 주택에 손해가 발생함으로써 1일이상 보험목적 내에 거주할 수 없게 된 경우</t>
+          <t>상해로 사망시</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>25만원</t>
+          <t>1억원</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>25만원</t>
+          <t>1억원</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -7726,17 +7738,17 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
-          <t>주택임시거주비Ⅱ(1-90일, 화재)</t>
+          <t>상해사망(갱신형)</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>화재, 폭발, 파열로 인해 보험증권에 기재된 주택에 손해가 발생함으로써 1일이상 보험목적 내에 거주할 수 없게 된 경우</t>
+          <t>상해로 사망시</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>25만원</t>
+          <t>1억원</t>
         </is>
       </c>
       <c r="W76" t="inlineStr"/>
@@ -7772,7 +7784,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -7782,22 +7794,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>화재배상책임담보</t>
+          <t>상해후유장해(갱신형)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>보험목적에 발생한 화재ㆍ폭발사고로 인하여 타인의 재물 또는 신체에 손해를 입힘으로써 법률상의 배상책임을 부담하는 경우</t>
+          <t>상해로 3%이상 후유장해시</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1억원 한도</t>
+          <t>300만원 ~ 1억원</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1억원 한도</t>
+          <t>300만원 ~ 1억원</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -7818,17 +7830,17 @@
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr">
         <is>
-          <t>화재배상책임담보</t>
+          <t>상해후유장해(갱신형)</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>보험목적에 발생한 화재ㆍ폭발사고로 인하여 타인의 재물 또는 신체에 손해를 입힘으로써 법률상의 배상책임을 부담하는 경우</t>
+          <t>상해로 3%이상 후유장해시</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>1억원 한도</t>
+          <t>300만원 ~ 1억원</t>
         </is>
       </c>
       <c r="W77" t="inlineStr"/>
@@ -7864,7 +7876,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -7874,22 +7886,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>화재상해사망후유장해</t>
+          <t>암진단Ⅱ(유사암제외)(갱신형)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>화재사고로 발생한 상해로 장해지급률이 3~100%에 해당하는 장해상태가 된 경우</t>
+          <t>암(유사암제외)로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>300만~1억원 한도</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>300만~1억원 한도</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -7910,17 +7922,17 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>화재상해사망후유장해</t>
+          <t>암진단Ⅱ(유사암제외)(갱신형)</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>화재사고로 발생한 상해로 장해지급률이 3~100%에 해당하는 장해상태가 된 경우</t>
+          <t>암(유사암제외)로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>300만~1억원 한도</t>
+          <t>1천만원</t>
         </is>
       </c>
       <c r="W78" t="inlineStr"/>
@@ -7956,7 +7968,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>(무)현대해상다이렉트H주택화재상해보험(Hi2601)</t>
+          <t>(무)현대해상다이렉트퍼펙트종합보험(Hi2601)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7964,20 +7976,24 @@
           <t>특약</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>유사암진단Ⅱ(갱신형)</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>화재사고로 발생한 상해로 사망한 경우</t>
+          <t>기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1억원</t>
+          <t>2백만원</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1억원</t>
+          <t>2백만원</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -7996,15 +8012,19 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>유사암진단Ⅱ(갱신형)</t>
+        </is>
+      </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>화재사고로 발생한 상해로 사망한 경우</t>
+          <t>기타피부암, 갑상선암, 제자리암 및 경계성종양으로 진단 확정된 경우</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>1억원</t>
+          <t>2백만원</t>
         </is>
       </c>
       <c r="W79" t="inlineStr"/>
@@ -9284,7 +9304,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9314,12 +9334,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8,688 원</t>
+          <t>8,649 원</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>8,688 원</t>
+          <t>8,649 원</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
@@ -9341,7 +9361,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -9361,22 +9381,22 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>8,688</t>
+          <t>8,649</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>8,688</t>
+          <t>8,649</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr"/>
@@ -9408,7 +9428,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9500,7 +9520,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9592,7 +9612,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9684,7 +9704,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9776,7 +9796,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>성공하는 Owner 재산종합보험 (무)2601</t>
+          <t>성공하는 Owner 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9868,7 +9888,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9898,12 +9918,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1,731 원</t>
+          <t>1,637 원</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1,731 원</t>
+          <t>1,637 원</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -9925,7 +9945,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -9945,22 +9965,22 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>1,731</t>
+          <t>1,637</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>1,731</t>
+          <t>1,637</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr"/>
@@ -9992,7 +10012,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10084,7 +10104,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10176,7 +10196,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10268,7 +10288,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>한화 BigPlus 재산종합보험 (무)2601</t>
+          <t>한화 BigPlus 재산종합보험 (무)2604</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10360,7 +10380,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10370,32 +10390,32 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>가족화재벌금</t>
+          <t>임차자배상책임(화재)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
+          <t>피보험자가 임차한 보험증권에 기재된 부동산이 화재로 인하여 없어지거나 망가짐으로써 그 부동산에 대하여 정당한 권리를 가진자에게 법률상 배상책임을 부담함으로써 손해를 입은 경우</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2,766 원</t>
+          <t>830 원</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2,766 원</t>
+          <t>830 원</t>
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
@@ -10417,42 +10437,42 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>가족화재벌금</t>
+          <t>임차자배상책임(화재)</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
+          <t>피보험자가 임차한 보험증권에 기재된 부동산이 화재로 인하여 없어지거나 망가짐으로써 그 부동산에 대하여 정당한 권리를 가진자에게 법률상 배상책임을 부담함으로써 손해를 입은 경우</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>2,766</t>
+          <t>830</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2,766</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr"/>
@@ -10484,7 +10504,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -10494,22 +10514,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>도난손해(주택)(실손전부형)</t>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -10530,17 +10550,17 @@
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr">
         <is>
-          <t>도난손해(주택)(실손전부형)</t>
+          <t>화재(폭발포함)배상책임Ⅱ</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>보험가입금액 한도</t>
+          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
         </is>
       </c>
       <c r="W105" t="inlineStr"/>
@@ -10576,7 +10596,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -10584,18 +10604,18 @@
           <t>특약</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
@@ -10612,17 +10632,13 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr">
-        <is>
-          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>대물(1사고당) : 보험가입금액 한도</t>
+        </is>
+      </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
@@ -10656,7 +10672,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -10666,22 +10682,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>주택화재임시거주비(4일이상)</t>
+          <t>화재손해</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>주택의 화재로 인해 보험의 목적 내에 거주할 수 없게 된 경우</t>
+          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -10702,17 +10718,17 @@
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr">
         <is>
-          <t>주택화재임시거주비(4일이상)</t>
+          <t>화재손해</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>주택의 화재로 인해 보험의 목적 내에 거주할 수 없게 된 경우</t>
+          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="W107" t="inlineStr"/>
@@ -10748,7 +10764,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10758,22 +10774,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ</t>
+          <t>가족화재벌금</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
+          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
+          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
+          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -10790,27 +10806,51 @@
         </is>
       </c>
       <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>롯데손보</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>(무) let:care 재물종합보험(2604)</t>
+        </is>
+      </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ</t>
+          <t>가족화재벌금</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>보험의 목적에서 발생한 화재 또는 폭발사고로 타인의 신체 또는 재물에 대한 법률상의 배상책임을 부담함으로써 입은 손해를 보상(단, 「다중이용업소의 안전관리에 관한 특별법」 제13조의2(화재배상책임보험 가입의무)에 따라 다중이용업주 및 다중이용업을 하려는 자가 가입한 의무보험에 해당하는 경우에는 피보험자의 과실여부를 불문함)</t>
+          <t>피보험자가 화재로 형법 제170조(실화) 혹은 동법 제171조(업무상실화, 중실화)에 따른 벌금형이 확정판결된 경우</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>대인(1인당) : 사망·후유장해 1억원 한도, 부상 2천만원 한도</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
+          <t>형법 제170조 : 1,500만원 한도형법 제171조 : 2,000만원 한도</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>2,766</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>2,766</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
@@ -10840,7 +10880,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10848,16 +10888,24 @@
           <t>특약</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>도난손해(주택)(실손전부형)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>대물(1사고당) : 보험가입금액 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>대물(1사고당) : 보험가입금액 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -10876,11 +10924,19 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>도난손해(주택)(실손전부형)</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>보험목적이 강도 또는 절도(미수 포함)로 인해 도난, 망가짐, 손상 및 파손된 손해를 입은 경우</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>대물(1사고당) : 보험가입금액 한도</t>
+          <t>보험가입금액 한도</t>
         </is>
       </c>
       <c r="W109" t="inlineStr"/>
@@ -10916,7 +10972,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>(무) let:care 재물종합보험(2601)</t>
+          <t>(무) let:care 화재배상책임보험(2604)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10926,24 +10982,16 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>화재손해(실손)</t>
+          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
+          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
@@ -10962,19 +11010,15 @@
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr">
         <is>
-          <t>화재손해(실손)</t>
+          <t>붕괴,침강및사태로인한재산손해(주택)(실손전부형)</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>화재(폭발, 파열 제외. 단,전용주택의 경우는 폭발, 파열포함)로 인해 직접손해 및 소방 ·피난손해가 발생한 경우</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>보험가입금액 한도</t>
-        </is>
-      </c>
+          <t>붕괴, 침강 및 사태로 인해 보험목적에 손해가 발생한 경우</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
@@ -17052,7 +17096,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -17109,7 +17153,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
@@ -17176,7 +17220,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -17268,7 +17312,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -17360,7 +17404,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -17452,7 +17496,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -17544,7 +17588,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>(무)참좋은화재플러스보장보험2601</t>
+          <t>(무)참좋은화재든든보장보험2601</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -17636,7 +17680,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -17646,32 +17690,32 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>가스사고배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1.5억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1.5억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>1,885 원</t>
+          <t>26,592 원</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1,885 원</t>
+          <t>26,592 원</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
@@ -17693,42 +17737,42 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>가스사고배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1.5억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>1,885</t>
+          <t>26,592</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>1,885</t>
+          <t>26,592</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>102.9</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>102.9</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr"/>
@@ -17760,7 +17804,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -17770,22 +17814,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태손해(실손보상, 동산제외)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태로 보험목적에 생긴 손해</t>
+          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
@@ -17806,17 +17850,17 @@
       <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태손해(실손보상, 동산제외)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>붕괴, 침강 및 사태로 보험목적에 생긴 손해</t>
+          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="V184" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W184" t="inlineStr"/>
@@ -17852,7 +17896,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -17862,22 +17906,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>주택(화재)건물재조달차액지원(실손)</t>
+          <t>배상책임종합보장(실손)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>보험목적(보험에 가입한 물건 중 주택건물을 말합니다)이 화재로 입은 손해</t>
+          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
@@ -17898,17 +17942,17 @@
       <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr">
         <is>
-          <t>주택(화재)건물재조달차액지원(실손)</t>
+          <t>배상책임종합보장(실손)</t>
         </is>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>보험목적(보험에 가입한 물건 중 주택건물을 말합니다)이 화재로 입은 손해</t>
+          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W185" t="inlineStr"/>
@@ -17944,7 +17988,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -17954,22 +17998,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>주택임시거주비(화재,붕괴,침강,사태)(1일이상)(실손)</t>
+          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>보험목적인 주택에서 발생한 화재(폭발포함),붕괴,침강,사태로 인하여 보험목적 내에서 거주할 수 없게 된 경우, 보험목적의 수리기간동안 지출한 숙박비 및 식비를 지급</t>
+          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
@@ -17990,17 +18034,17 @@
       <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr">
         <is>
-          <t>주택임시거주비(화재,붕괴,침강,사태)(1일이상)(실손)</t>
+          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
         </is>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>보험목적인 주택에서 발생한 화재(폭발포함),붕괴,침강,사태로 인하여 보험목적 내에서 거주할 수 없게 된 경우, 보험목적의 수리기간동안 지출한 숙박비 및 식비를 지급</t>
+          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
         </is>
       </c>
       <c r="V186" t="inlineStr">
         <is>
-          <t>1일당 보험가입금액(10만)한도 내 실손보상(사고일로부터 90일한도)</t>
+          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W186" t="inlineStr"/>
@@ -18036,7 +18080,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -18046,22 +18090,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>재산손해종합보장(실손보상)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
@@ -18082,17 +18126,17 @@
       <c r="S187" t="inlineStr"/>
       <c r="T187" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>재산손해종합보장(실손보상)</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(1억)한도 내 실손보상</t>
         </is>
       </c>
       <c r="W187" t="inlineStr"/>
@@ -18128,7 +18172,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>(무)참좋은화재든든보장보험2601</t>
+          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -18138,22 +18182,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>화재손해(실손보상)</t>
+          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>① 화재에 따른 직접손해② 화재에 따른 소방손해(화재진압과정에서 발생하는 손해)③ 화재에 따른 피난손해(피난지에서 5일동안 생긴 위 ①, ②의 손해)④ 잔존물 제거비용(화재발생 후 사고현장에서 잔존물의 해체비용, 청소비용, 차에 싣는 비용을 화재손해액의 10%이내에서 실비지급. 단, 화재손해 및 잔존물제거비용의 합계액은 이 담보의 보험가입금액을 한도로 지급)</t>
+          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
@@ -18174,17 +18218,17 @@
       <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr">
         <is>
-          <t>화재손해(실손보상)</t>
+          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
         </is>
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>① 화재에 따른 직접손해② 화재에 따른 소방손해(화재진압과정에서 발생하는 손해)③ 화재에 따른 피난손해(피난지에서 5일동안 생긴 위 ①, ②의 손해)④ 잔존물 제거비용(화재발생 후 사고현장에서 잔존물의 해체비용, 청소비용, 차에 싣는 비용을 화재손해액의 10%이내에서 실비지급. 단, 화재손해 및 잔존물제거비용의 합계액은 이 담보의 보험가입금액을 한도로 지급)</t>
+          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
         </is>
       </c>
       <c r="V188" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
         </is>
       </c>
       <c r="W188" t="inlineStr"/>
@@ -18220,7 +18264,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -18230,32 +18274,32 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>가스사고배상책임Ⅱ(실손)</t>
+          <t>뇌혈관질환진단비</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
+          <t>피보험자가 보험기간 중 뇌혈관질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>보험가입금액(1.5억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>보험가입금액(1.5억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>26,592 원</t>
+          <t>97,490 원</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>26,592 원</t>
+          <t>82,750 원</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -18277,42 +18321,42 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>가스사고배상책임Ⅱ(실손)</t>
+          <t>뇌혈관질환진단비</t>
         </is>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>보험증권에 기재된 시설 내에서 가스를 소유, 사용, 관리 중에 가스사고로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해를 아래의 한도 내에서 실손해액 지급</t>
+          <t>피보험자가 보험기간 중 뇌혈관질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>보험가입금액(1.5억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>26,592</t>
+          <t>97,490</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>26,592</t>
+          <t>82,750</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr"/>
@@ -18344,7 +18388,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -18354,22 +18398,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>피보험자가 보험기간 중 상해사고로 사망한 경우 보험가입금액 지급</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1억원)</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1억원)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
@@ -18390,17 +18434,17 @@
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr">
         <is>
-          <t>가족화재벌금(실손)</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>피보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
+          <t>피보험자가 보험기간 중 상해사고로 사망한 경우 보험가입금액 지급</t>
         </is>
       </c>
       <c r="V190" t="inlineStr">
         <is>
-          <t>보험가입금액(2천만)한도 내 실손보상</t>
+          <t>보험가입금액(1억원)</t>
         </is>
       </c>
       <c r="W190" t="inlineStr"/>
@@ -18436,7 +18480,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -18446,22 +18490,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>배상책임종합보장(실손)</t>
+          <t>암진단비Ⅱ(유사암제외)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
+          <t>피보험자가 보장개시일(보험계약일로부터 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정시 가입금액 지급 (최초 1회에 한함, 기타피부암, 갑상선암, 제자리암, 경계성종양은 보장하지 않음)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1,000만원)</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1,000만원)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -18482,17 +18526,17 @@
       <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr">
         <is>
-          <t>배상책임종합보장(실손)</t>
+          <t>암진단비Ⅱ(유사암제외)</t>
         </is>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>피보험자가 소유, 사용, 관리하는 보험증권에 기재된 시설 및 그 시설의 용도에 따른 업무수행으로 생긴 우연한 사고로 타인의 신체에 장해를 입히거나 재물에 손해를 입혀 법률상 손해배상책임을 부담함으로써 입은 실손해액 지급</t>
+          <t>피보험자가 보장개시일(보험계약일로부터 90일이 지난날의 다음날) 이후에 암(유사암제외)으로 진단확정시 가입금액 지급 (최초 1회에 한함, 기타피부암, 갑상선암, 제자리암, 경계성종양은 보장하지 않음)</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(1,000만원)</t>
         </is>
       </c>
       <c r="W191" t="inlineStr"/>
@@ -18528,7 +18572,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -18538,22 +18582,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
+          <t>항암방사선약물치료비(유사암포함)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
+          <t>*암(유사암제외)으로 항암방사선 또는 항암약물치료시 - 보장개시일(계약일로부터 90일이 지난날의 다음날) 이후에 진단확정된 암(유사암제외)의 직접치료를 목적으로 항암방사선 또는 항암약물치료시 가입금액 지급 (최초1회한) *제자리암, 경계성종양, 기타피부암, 갑상선암으로 항암방사선 또는 항암약물치료시 - 계약일 이후에 진단확정된 제자리암, 경계성종양, 기타피부암, 갑상선암의 직접치료를 목적으로 항암방사선, 약물치료시 가입금액의 20% 지급 (각 1회에 한함)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
@@ -18574,17 +18618,17 @@
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr">
         <is>
-          <t>일반·공장(재산손해)건물재조달차액지원(실손)</t>
+          <t>항암방사선약물치료비(유사암포함)</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>재산손해종합보장에서 정한 위험으로 보험의 목적(건물)에 손해가 발생하는 경우</t>
+          <t>*암(유사암제외)으로 항암방사선 또는 항암약물치료시 - 보장개시일(계약일로부터 90일이 지난날의 다음날) 이후에 진단확정된 암(유사암제외)의 직접치료를 목적으로 항암방사선 또는 항암약물치료시 가입금액 지급 (최초1회한) *제자리암, 경계성종양, 기타피부암, 갑상선암으로 항암방사선 또는 항암약물치료시 - 계약일 이후에 진단확정된 제자리암, 경계성종양, 기타피부암, 갑상선암의 직접치료를 목적으로 항암방사선, 약물치료시 가입금액의 20% 지급 (각 1회에 한함)</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>손해가 생긴 때와 곳에서의 「재조달가액」과 「보험가액」의 차액을 보험가입금액(1억)한도 내 실손보상</t>
+          <t>보험가입금액(2,000만원)</t>
         </is>
       </c>
       <c r="W192" t="inlineStr"/>
@@ -18620,7 +18664,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -18630,24 +18674,16 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>재산손해종합보장(실손보상)</t>
+          <t>허혈심장질환진단비</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
-        </is>
-      </c>
+          <t>피보험자가 보험기간 중 허혈심장질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
@@ -18666,19 +18702,15 @@
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr">
         <is>
-          <t>재산손해종합보장(실손보상)</t>
+          <t>허혈심장질환진단비</t>
         </is>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>보험의 목적에 급격하고 우연하게 발생한 직접적인 재산손해</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>보험가입금액(1억)한도 내 실손보상</t>
-        </is>
-      </c>
+          <t>피보험자가 보험기간 중 허혈심장질환으로 진단확정된 경우 보험가입금액을 지급(1회한, 가입 후 1년미만시 가입금액의 50%지급)</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr"/>
       <c r="W193" t="inlineStr"/>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr"/>
@@ -18712,7 +18744,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>(무)드림빅비즈니스보장보험2601(1종)</t>
+          <t>(무)드림빅비즈니스보장보험2601(2종)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -18722,22 +18754,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
@@ -18754,27 +18786,51 @@
         </is>
       </c>
       <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>(무)참좋은화재플러스보장보험2604</t>
+        </is>
+      </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>화재(폭발포함)배상책임Ⅱ(실손)</t>
+          <t>가족화재벌금(실손)</t>
         </is>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>보험증권에 목적물(보험증권상의 소재지의 보장지역(면적) 내에서 피보험자가 소유, 사용 또는 관리하는 물건)에서 발생한 화재(폭발포함)로 인해 타인의 신체 및 재물에 손해에 대한 법률상의 손해배상책임을 부담함으로써 입은 손해</t>
+          <t>보험자 본인 및 가족이 보험기간 중에 형법 제170조 또는 제171조에서 정한 실화, 업무상실화, 중실화에 따른 벌금형이 확정된 경우</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
         <is>
-          <t>보험가입금액(대인 1억, 대물 1억) 한도내 실손보상</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr"/>
-      <c r="X194" t="inlineStr"/>
-      <c r="Y194" t="inlineStr"/>
-      <c r="Z194" t="inlineStr"/>
+          <t>보험가입금액(2천만)한도 내 실손보상</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>1,885</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>1,885</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr"/>
       <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="inlineStr"/>
@@ -18804,7 +18860,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -18824,12 +18880,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>(「형법」 제170조(실화)에 의한 벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조(업무상실화, 중실화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
+          <t>(「형법」 제170조 (실화)에 의한  벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조 (업무상실화, 중실 화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>(「형법」 제170조(실화)에 의한 벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조(업무상실화, 중실화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
+          <t>(「형법」 제170조 (실화)에 의한  벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조 (업무상실화, 중실 화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -18861,7 +18917,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="T195" t="inlineStr">
@@ -18876,7 +18932,7 @@
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>(「형법」 제170조(실화)에 의한 벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조(업무상실화, 중실화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
+          <t>(「형법」 제170조 (실화)에 의한  벌금) 1사고당 벌금액(단, 1,500만원 한도) (「형법」 제171조 (업무상실화, 중실 화)에 의한 벌금) 1사고당 벌금액(단, 2,000만원 한도)</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
@@ -18928,7 +18984,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -19020,7 +19076,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -19112,7 +19168,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -19204,7 +19260,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -19296,7 +19352,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -19388,7 +19444,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>(무)AXA생활안심종합보험Ⅱ2601</t>
+          <t>(무)AXA생활안심종합보험Ⅱ2604</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
